--- a/Data/t17.2.xlsx
+++ b/Data/t17.2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F199"/>
+  <dimension ref="A1:F210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6400,6 +6400,336 @@
         <v>5.4</v>
       </c>
     </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Ensino Médio</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>IDEB</t>
+        </is>
+      </c>
+      <c r="F200" t="n">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Ensino Médio</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Privada</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>IDEB</t>
+        </is>
+      </c>
+      <c r="F201" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Ensino Médio</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>IDEB</t>
+        </is>
+      </c>
+      <c r="F202" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Fundamental - Anos Finais</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>IDEB</t>
+        </is>
+      </c>
+      <c r="F203" t="n">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Fundamental - Anos Finais</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Privada</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>IDEB</t>
+        </is>
+      </c>
+      <c r="F204" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Fundamental - Anos Finais</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Pública</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>IDEB</t>
+        </is>
+      </c>
+      <c r="F205" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Fundamental - Anos Finais</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>IDEB</t>
+        </is>
+      </c>
+      <c r="F206" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Fundamental - Anos Iniciais</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Estadual</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>IDEB</t>
+        </is>
+      </c>
+      <c r="F207" t="n">
+        <v>5.7</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Fundamental - Anos Iniciais</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Privada</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>IDEB</t>
+        </is>
+      </c>
+      <c r="F208" t="n">
+        <v>6.7</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Fundamental - Anos Iniciais</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Pública</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>IDEB</t>
+        </is>
+      </c>
+      <c r="F209" t="n">
+        <v>5.4</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>01/01/2025</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Sergipe</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Fundamental - Anos Iniciais</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>IDEB</t>
+        </is>
+      </c>
+      <c r="F210" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
